--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncDetailPlatformExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncDetailPlatformExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
     <t>{.outstockQty}</t>
   </si>
   <si>
-    <t>{.platformSkuName}</t>
+    <t>{.platformProductName}</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1070,7 @@
     <col min="6" max="6" width="14.625" customWidth="1"/>
     <col min="7" max="7" width="16.75" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="20.25" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="18.25" customWidth="1"/>
     <col min="11" max="11" width="14.75" customWidth="1"/>
     <col min="12" max="12" width="18.25" customWidth="1"/>
@@ -1078,7 +1078,7 @@
     <col min="14" max="14" width="16.375" customWidth="1"/>
     <col min="15" max="15" width="11.375" customWidth="1"/>
     <col min="16" max="16" width="17.75" customWidth="1"/>
-    <col min="17" max="17" width="17.875" customWidth="1"/>
+    <col min="17" max="17" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
